--- a/poker_play_log.xlsx
+++ b/poker_play_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="21.44140625" customWidth="1" min="1" max="1"/>
@@ -597,6 +597,34 @@
         <v>800</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:43:56</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>80</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>役なし</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>役なし</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>負け</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/poker_play_log.xlsx
+++ b/poker_play_log.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="144" yWindow="204" windowWidth="12780" windowHeight="13332" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PlayLog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlayLog" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -419,8 +419,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2" outlineLevelCol="0"/>
   <cols>
     <col width="21.44140625" customWidth="1" min="1" max="1"/>
   </cols>
@@ -625,6 +625,230 @@
         <v>20</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:49:39</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>フォーカード</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ワンペア</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>勝ち</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:50:31</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>90</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ワンペア</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ワンペア</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>勝ち</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:52:41</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>役なし</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ワンペア</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>負け</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:52:49</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ワンペア</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>役なし</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>勝ち</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:53:45</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>役なし</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ワンペア</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>負け</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:53:52</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ストレート</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>役なし</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>勝ち</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:02:18</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>90</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ツーペア</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ワンペア</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>勝ち</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:03:14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>役なし</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>役なし</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>負け</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
